--- a/bug-reports/Bug_Report_Test_Drive.xlsx
+++ b/bug-reports/Bug_Report_Test_Drive.xlsx
@@ -212,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -260,14 +260,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -280,12 +280,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1328,7 +1322,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
@@ -1539,7 +1533,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>Defects: 21. Critical — 1, Major — 11, Minor — 8, Trivial — 1. Priority High — 9, Medium — 6, Low — 6. Improvements kept out of the defect list: 2. Every defect reproduces always, 5 out of 5.</t>
+          <t>Defects: 21. Critical — 1, Major — 11, Minor — 8, Trivial — 1. Priority is left blank in every report. Improvements kept out of the defect list: 2. Every defect reproduces always, 5 out of 5.</t>
         </is>
       </c>
     </row>
@@ -1648,11 +1642,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D2" s="19" t="inlineStr"/>
       <c r="E2" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1690,11 +1680,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D3" s="19" t="inlineStr"/>
       <c r="E3" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1732,11 +1718,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D4" s="19" t="inlineStr"/>
       <c r="E4" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1774,11 +1756,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D5" s="19" t="inlineStr"/>
       <c r="E5" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1816,11 +1794,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D6" s="19" t="inlineStr"/>
       <c r="E6" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1858,11 +1832,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1900,11 +1870,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D8" s="19" t="inlineStr"/>
       <c r="E8" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1942,11 +1908,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D9" s="19" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1984,11 +1946,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D10" s="19" t="inlineStr"/>
       <c r="E10" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2026,11 +1984,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D11" s="19" t="inlineStr"/>
       <c r="E11" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2068,11 +2022,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D12" s="19" t="inlineStr"/>
       <c r="E12" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2110,11 +2060,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="D13" s="19" t="inlineStr"/>
       <c r="E13" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2152,11 +2098,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="D14" s="19" t="inlineStr"/>
       <c r="E14" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2194,11 +2136,7 @@
           <t>Trivial</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D15" s="19" t="inlineStr"/>
       <c r="E15" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2236,11 +2174,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D16" s="19" t="inlineStr"/>
       <c r="E16" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2278,11 +2212,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="D17" s="19" t="inlineStr"/>
       <c r="E17" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2320,11 +2250,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="D18" s="19" t="inlineStr"/>
       <c r="E18" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2362,11 +2288,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="D19" s="19" t="inlineStr"/>
       <c r="E19" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2404,11 +2326,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D20" s="19" t="inlineStr"/>
       <c r="E20" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2446,11 +2364,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D21" s="19" t="inlineStr"/>
       <c r="E21" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2488,11 +2402,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D22" s="19" t="inlineStr"/>
       <c r="E22" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2535,12 +2445,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>BUG-001   [Page] The browser tab has no page title</t>
         </is>
       </c>
-      <c r="B1" s="20" t="n"/>
+      <c r="B1" s="21" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -2596,7 +2506,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -2608,11 +2518,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -2634,7 +2540,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2690,7 @@
           <t>BUG-002   [Choose the model] "Cayenne 400" is shown as a Mercedes-Benz hatchback</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n"/>
+      <c r="B30" s="21" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -2852,11 +2758,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -2878,7 +2780,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -3055,7 +2957,7 @@
           <t>BUG-003   [GLC 250D 4MATIC] The Engine list contains OutOfMemoryError</t>
         </is>
       </c>
-      <c r="B84" s="20" t="n"/>
+      <c r="B84" s="21" t="n"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -3123,11 +3025,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B90" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B90" s="5" t="inlineStr"/>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
@@ -3149,7 +3047,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3223,7 @@
           <t>BUG-004   [GLC 250D 4MATIC] Leaving the engine unchanged submits Petrol 2.2</t>
         </is>
       </c>
-      <c r="B138" s="20" t="n"/>
+      <c r="B138" s="21" t="n"/>
     </row>
     <row r="139" ht="24" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
@@ -3393,11 +3291,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B144" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B144" s="5" t="inlineStr"/>
     </row>
     <row r="145" ht="24" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
@@ -3419,7 +3313,7 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3491,7 @@
           <t>BUG-005   [Confirmation] Engine OutOfMemoryError is shown as {transmission}</t>
         </is>
       </c>
-      <c r="B192" s="20" t="n"/>
+      <c r="B192" s="21" t="n"/>
     </row>
     <row r="193" ht="24" customHeight="1">
       <c r="A193" s="4" t="inlineStr">
@@ -3665,11 +3559,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B198" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B198" s="5" t="inlineStr"/>
     </row>
     <row r="199" ht="24" customHeight="1">
       <c r="A199" s="4" t="inlineStr">
@@ -3691,7 +3581,7 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -3865,12 +3755,12 @@
     <row r="242" ht="15" customHeight="1"/>
     <row r="243" ht="15" customHeight="1"/>
     <row r="246" ht="28" customHeight="1">
-      <c r="A246" s="19" t="inlineStr">
+      <c r="A246" s="20" t="inlineStr">
         <is>
           <t>BUG-006   [Wizard] Step numbers run 1, 2, 4, 5</t>
         </is>
       </c>
-      <c r="B246" s="20" t="n"/>
+      <c r="B246" s="21" t="n"/>
     </row>
     <row r="247" ht="24" customHeight="1">
       <c r="A247" s="4" t="inlineStr">
@@ -3926,7 +3816,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B251" s="21" t="inlineStr">
+      <c r="B251" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -3938,11 +3828,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B252" s="28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="B252" s="5" t="inlineStr"/>
     </row>
     <row r="253" ht="24" customHeight="1">
       <c r="A253" s="4" t="inlineStr">
@@ -3964,7 +3850,7 @@
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4027,7 @@
           <t>BUG-007   [Wizard] There is no way back to the previous step</t>
         </is>
       </c>
-      <c r="B300" s="20" t="n"/>
+      <c r="B300" s="21" t="n"/>
     </row>
     <row r="301" ht="24" customHeight="1">
       <c r="A301" s="4" t="inlineStr">
@@ -4209,11 +4095,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B306" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B306" s="5" t="inlineStr"/>
     </row>
     <row r="307" ht="24" customHeight="1">
       <c r="A307" s="4" t="inlineStr">
@@ -4235,7 +4117,7 @@
       </c>
       <c r="B308" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -4407,12 +4289,12 @@
     <row r="350" ht="15" customHeight="1"/>
     <row r="351" ht="15" customHeight="1"/>
     <row r="354" ht="28" customHeight="1">
-      <c r="A354" s="29" t="inlineStr">
+      <c r="A354" s="27" t="inlineStr">
         <is>
           <t>BUG-008   [Contacts] An empty registration can be booked, and the summary shows field templates</t>
         </is>
       </c>
-      <c r="B354" s="20" t="n"/>
+      <c r="B354" s="21" t="n"/>
     </row>
     <row r="355" ht="24" customHeight="1">
       <c r="A355" s="4" t="inlineStr">
@@ -4468,7 +4350,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B359" s="30" t="inlineStr">
+      <c r="B359" s="28" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -4480,11 +4362,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B360" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B360" s="5" t="inlineStr"/>
     </row>
     <row r="361" ht="24" customHeight="1">
       <c r="A361" s="4" t="inlineStr">
@@ -4506,7 +4384,7 @@
       </c>
       <c r="B362" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4649,7 @@
           <t>BUG-009   [Contacts] Spaces-only values are accepted and the name disappears from the summary</t>
         </is>
       </c>
-      <c r="B476" s="20" t="n"/>
+      <c r="B476" s="21" t="n"/>
     </row>
     <row r="477" ht="24" customHeight="1">
       <c r="A477" s="4" t="inlineStr">
@@ -4839,11 +4717,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B482" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B482" s="5" t="inlineStr"/>
     </row>
     <row r="483" ht="24" customHeight="1">
       <c r="A483" s="4" t="inlineStr">
@@ -4865,7 +4739,7 @@
       </c>
       <c r="B484" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -5041,7 +4915,7 @@
           <t>BUG-010   [Contacts] Age accepts a negative number</t>
         </is>
       </c>
-      <c r="B530" s="20" t="n"/>
+      <c r="B530" s="21" t="n"/>
     </row>
     <row r="531" ht="24" customHeight="1">
       <c r="A531" s="4" t="inlineStr">
@@ -5109,11 +4983,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B536" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B536" s="5" t="inlineStr"/>
     </row>
     <row r="537" ht="24" customHeight="1">
       <c r="A537" s="4" t="inlineStr">
@@ -5135,7 +5005,7 @@
       </c>
       <c r="B538" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5269,7 @@
           <t>BUG-011   [Contacts] The phone field accepts letters</t>
         </is>
       </c>
-      <c r="B652" s="20" t="n"/>
+      <c r="B652" s="21" t="n"/>
     </row>
     <row r="653" ht="24" customHeight="1">
       <c r="A653" s="4" t="inlineStr">
@@ -5467,11 +5337,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B658" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B658" s="5" t="inlineStr"/>
     </row>
     <row r="659" ht="24" customHeight="1">
       <c r="A659" s="4" t="inlineStr">
@@ -5493,7 +5359,7 @@
       </c>
       <c r="B660" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5536,7 @@
           <t>BUG-012   [Contacts] Name fields accept digits and symbols</t>
         </is>
       </c>
-      <c r="B706" s="20" t="n"/>
+      <c r="B706" s="21" t="n"/>
     </row>
     <row r="707" ht="24" customHeight="1">
       <c r="A707" s="4" t="inlineStr">
@@ -5738,11 +5604,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B712" s="28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="B712" s="5" t="inlineStr"/>
     </row>
     <row r="713" ht="24" customHeight="1">
       <c r="A713" s="4" t="inlineStr">
@@ -5764,7 +5626,7 @@
       </c>
       <c r="B714" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5802,7 @@
           <t>BUG-013   [Confirmation] A long name with no spaces runs off the page</t>
         </is>
       </c>
-      <c r="B760" s="20" t="n"/>
+      <c r="B760" s="21" t="n"/>
     </row>
     <row r="761" ht="24" customHeight="1">
       <c r="A761" s="4" t="inlineStr">
@@ -6008,11 +5870,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B766" s="28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="B766" s="5" t="inlineStr"/>
     </row>
     <row r="767" ht="24" customHeight="1">
       <c r="A767" s="4" t="inlineStr">
@@ -6034,7 +5892,7 @@
       </c>
       <c r="B768" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6051,12 @@
     <row r="798" ht="15" customHeight="1"/>
     <row r="799" ht="15" customHeight="1"/>
     <row r="802" ht="28" customHeight="1">
-      <c r="A802" s="31" t="inlineStr">
+      <c r="A802" s="29" t="inlineStr">
         <is>
           <t>BUG-014   [Confirmation] The configuration line has a space before the comma</t>
         </is>
       </c>
-      <c r="B802" s="20" t="n"/>
+      <c r="B802" s="21" t="n"/>
     </row>
     <row r="803" ht="24" customHeight="1">
       <c r="A803" s="4" t="inlineStr">
@@ -6254,7 +6112,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B807" s="32" t="inlineStr">
+      <c r="B807" s="30" t="inlineStr">
         <is>
           <t>Trivial</t>
         </is>
@@ -6266,11 +6124,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B808" s="22" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="B808" s="5" t="inlineStr"/>
     </row>
     <row r="809" ht="24" customHeight="1">
       <c r="A809" s="4" t="inlineStr">
@@ -6292,7 +6146,7 @@
       </c>
       <c r="B810" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -6462,12 +6316,12 @@
     <row r="852" ht="15" customHeight="1"/>
     <row r="853" ht="15" customHeight="1"/>
     <row r="856" ht="28" customHeight="1">
-      <c r="A856" s="19" t="inlineStr">
+      <c r="A856" s="20" t="inlineStr">
         <is>
           <t>BUG-015   [Copy] Labels and sentences in the wizard contain grammar errors</t>
         </is>
       </c>
-      <c r="B856" s="20" t="n"/>
+      <c r="B856" s="21" t="n"/>
     </row>
     <row r="857" ht="24" customHeight="1">
       <c r="A857" s="4" t="inlineStr">
@@ -6523,7 +6377,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B861" s="21" t="inlineStr">
+      <c r="B861" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -6535,11 +6389,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B862" s="22" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="B862" s="5" t="inlineStr"/>
     </row>
     <row r="863" ht="24" customHeight="1">
       <c r="A863" s="4" t="inlineStr">
@@ -6561,7 +6411,7 @@
       </c>
       <c r="B864" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -6791,7 +6641,7 @@
           <t>BUG-016   [Choose the model] Fast clicks on the arrow stack several cars on top of each other</t>
         </is>
       </c>
-      <c r="B944" s="20" t="n"/>
+      <c r="B944" s="21" t="n"/>
     </row>
     <row r="945" ht="24" customHeight="1">
       <c r="A945" s="4" t="inlineStr">
@@ -6859,11 +6709,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B950" s="28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="B950" s="5" t="inlineStr"/>
     </row>
     <row r="951" ht="24" customHeight="1">
       <c r="A951" s="4" t="inlineStr">
@@ -6885,7 +6731,7 @@
       </c>
       <c r="B952" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -7056,12 +6902,12 @@
     <row r="994" ht="15" customHeight="1"/>
     <row r="995" ht="15" customHeight="1"/>
     <row r="998" ht="28" customHeight="1">
-      <c r="A998" s="19" t="inlineStr">
+      <c r="A998" s="20" t="inlineStr">
         <is>
           <t>BUG-017   [Contacts] The field caption is not tied to the field and does not focus it</t>
         </is>
       </c>
-      <c r="B998" s="20" t="n"/>
+      <c r="B998" s="21" t="n"/>
     </row>
     <row r="999" ht="24" customHeight="1">
       <c r="A999" s="4" t="inlineStr">
@@ -7117,7 +6963,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B1003" s="21" t="inlineStr">
+      <c r="B1003" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7129,11 +6975,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B1004" s="28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="B1004" s="5" t="inlineStr"/>
     </row>
     <row r="1005" ht="24" customHeight="1">
       <c r="A1005" s="4" t="inlineStr">
@@ -7155,7 +6997,7 @@
       </c>
       <c r="B1006" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -7326,12 +7168,12 @@
     <row r="1048" ht="15" customHeight="1"/>
     <row r="1049" ht="15" customHeight="1"/>
     <row r="1052" ht="28" customHeight="1">
-      <c r="A1052" s="19" t="inlineStr">
+      <c r="A1052" s="20" t="inlineStr">
         <is>
           <t>BUG-018   [Choose the model] The carousel arrows cannot be operated from the keyboard</t>
         </is>
       </c>
-      <c r="B1052" s="20" t="n"/>
+      <c r="B1052" s="21" t="n"/>
     </row>
     <row r="1053" ht="24" customHeight="1">
       <c r="A1053" s="4" t="inlineStr">
@@ -7387,7 +7229,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B1057" s="21" t="inlineStr">
+      <c r="B1057" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7399,11 +7241,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B1058" s="28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="B1058" s="5" t="inlineStr"/>
     </row>
     <row r="1059" ht="24" customHeight="1">
       <c r="A1059" s="4" t="inlineStr">
@@ -7425,7 +7263,7 @@
       </c>
       <c r="B1060" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -7552,12 +7390,12 @@
       </c>
     </row>
     <row r="1072" ht="28" customHeight="1">
-      <c r="A1072" s="19" t="inlineStr">
+      <c r="A1072" s="20" t="inlineStr">
         <is>
           <t>BUG-019   [Page] Images have no text alternative, and the page language is not set</t>
         </is>
       </c>
-      <c r="B1072" s="20" t="n"/>
+      <c r="B1072" s="21" t="n"/>
     </row>
     <row r="1073" ht="24" customHeight="1">
       <c r="A1073" s="4" t="inlineStr">
@@ -7613,7 +7451,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B1077" s="21" t="inlineStr">
+      <c r="B1077" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7625,11 +7463,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B1078" s="22" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="B1078" s="5" t="inlineStr"/>
     </row>
     <row r="1079" ht="24" customHeight="1">
       <c r="A1079" s="4" t="inlineStr">
@@ -7651,7 +7485,7 @@
       </c>
       <c r="B1080" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -7821,12 +7655,12 @@
     <row r="1122" ht="15" customHeight="1"/>
     <row r="1123" ht="15" customHeight="1"/>
     <row r="1126" ht="28" customHeight="1">
-      <c r="A1126" s="19" t="inlineStr">
+      <c r="A1126" s="20" t="inlineStr">
         <is>
           <t>BUG-020   [Thank you] After Book, the screen does not show what was booked</t>
         </is>
       </c>
-      <c r="B1126" s="20" t="n"/>
+      <c r="B1126" s="21" t="n"/>
     </row>
     <row r="1127" ht="24" customHeight="1">
       <c r="A1127" s="4" t="inlineStr">
@@ -7882,7 +7716,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B1131" s="21" t="inlineStr">
+      <c r="B1131" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7894,11 +7728,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B1132" s="22" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="B1132" s="5" t="inlineStr"/>
     </row>
     <row r="1133" ht="24" customHeight="1">
       <c r="A1133" s="4" t="inlineStr">
@@ -7920,7 +7750,7 @@
       </c>
       <c r="B1134" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -8091,12 +7921,12 @@
     <row r="1176" ht="15" customHeight="1"/>
     <row r="1177" ht="15" customHeight="1"/>
     <row r="1180" ht="28" customHeight="1">
-      <c r="A1180" s="19" t="inlineStr">
+      <c r="A1180" s="20" t="inlineStr">
         <is>
           <t>BUG-021   [Page] The page loads jQuery 1.11.1, and that line is no longer supported</t>
         </is>
       </c>
-      <c r="B1180" s="20" t="n"/>
+      <c r="B1180" s="21" t="n"/>
     </row>
     <row r="1181" ht="24" customHeight="1">
       <c r="A1181" s="4" t="inlineStr">
@@ -8152,7 +7982,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B1185" s="21" t="inlineStr">
+      <c r="B1185" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -8164,11 +7994,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="B1186" s="22" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="B1186" s="5" t="inlineStr"/>
     </row>
     <row r="1187" ht="24" customHeight="1">
       <c r="A1187" s="4" t="inlineStr">
@@ -8190,7 +8016,7 @@
       </c>
       <c r="B1188" s="5" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8222,7 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>IMP-001   The wizard never asks for a date, a time, or a dealership</t>
         </is>
@@ -8439,7 +8265,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>IMP-002   Book does not ask for consent to use the name, age, and phone number</t>
         </is>
@@ -8534,7 +8360,7 @@
           <t>S500 Cabriolet AMG is a cabriolet, GLC 250D 4MATIC is an SUV, and CLA SB Standard is a shooting brake. The body style in the photo matches the caption.</t>
         </is>
       </c>
-      <c r="C2" s="34" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
@@ -8551,7 +8377,7 @@
           <t>The forward arrow cycles through S500 Cabriolet AMG, Cayenne 400, GLC 250D 4MATIC, and CLA SB Standard. The back arrow from the first model opens the last one.</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
@@ -8568,7 +8394,7 @@
           <t>S500 Cabriolet AMG: Petrol 3.0 and Petrol 3.5, transmission Automatic only. CLA SB Standard: Petrol 2.0 and Diesel 2.0, Automatic and Manual.</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
@@ -8585,7 +8411,7 @@
           <t>Last name Иванов, first name Иван, and middle name Иванович appear in the summary without corruption.</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
@@ -8602,7 +8428,7 @@
           <t>The value &lt;script&gt;alert(1)&lt;/script&gt; in the first name is shown as text. No dialog appeared.</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
@@ -8619,7 +8445,7 @@
           <t>Ivanov / Ivan / Ivanovich / 30 / +375291234567 for S500 Cabriolet AMG reaches the thank-you screen. Copy issues on that path are BUG-014 and BUG-015.</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
@@ -8636,7 +8462,7 @@
           <t>The console had no messages on load. At 1440×900 and at 1280×800, a name of ordinary length does not cause a horizontal scrollbar.</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>

--- a/bug-reports/Bug_Report_Test_Drive.xlsx
+++ b/bug-reports/Bug_Report_Test_Drive.xlsx
@@ -1802,7 +1802,7 @@
       </c>
       <c r="F6" s="18" t="inlineStr">
         <is>
-          <t>Confirm the data</t>
+          <t>Step 4. Confirm the data</t>
         </is>
       </c>
       <c r="G6" s="18" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F9" s="18" t="inlineStr">
         <is>
-          <t>Contact details and confirmation</t>
+          <t>Step 3. Contact details and confirmation</t>
         </is>
       </c>
       <c r="G9" s="18" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>Contact details and confirmation</t>
+          <t>Step 3. Contact details and confirmation</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F14" s="18" t="inlineStr">
         <is>
-          <t>Confirm the data</t>
+          <t>Step 4. Confirm the data</t>
         </is>
       </c>
       <c r="G14" s="18" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="F15" s="18" t="inlineStr">
         <is>
-          <t>Confirm the data</t>
+          <t>Step 4. Confirm the data</t>
         </is>
       </c>
       <c r="G15" s="18" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>Confirm the data</t>
+          <t>Step 4. Confirm the data</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="B358" s="5" t="inlineStr">
         <is>
-          <t>Contact details and confirmation</t>
+          <t>Step 3. Contact details and confirmation</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B480" s="5" t="inlineStr">
         <is>
-          <t>Contact details and confirmation</t>
+          <t>Step 3. Contact details and confirmation</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="B764" s="5" t="inlineStr">
         <is>
-          <t>Confirm the data</t>
+          <t>Step 4. Confirm the data</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="B806" s="5" t="inlineStr">
         <is>
-          <t>Confirm the data</t>
+          <t>Step 4. Confirm the data</t>
         </is>
       </c>
     </row>

--- a/bug-reports/Bug_Report_Test_Drive.xlsx
+++ b/bug-reports/Bug_Report_Test_Drive.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Passed checks" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Register'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Register'!$A$1:$H$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Register'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Passed checks'!$A$1:$C$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Passed checks'!$1:$1</definedName>
@@ -1533,7 +1533,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>Defects: 21. Critical — 1, Major — 11, Minor — 8, Trivial — 1. Priority is left blank in every report. Improvements kept out of the defect list: 2. Every defect reproduces always, 5 out of 5.</t>
+          <t>Defects: 20. Critical — 1, Major — 11, Minor — 7, Trivial — 1. Priority is left blank in every report. Improvements kept out of the defect list: 2. Every defect reproduces always, 5 out of 5.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2386,46 +2386,8 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>BUG-021</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>[Page] The page loads jQuery 1.11.1, and that line is no longer supported</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr"/>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>Third-party libraries</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>Always (5/5)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H22"/>
+  <autoFilter ref="A1:H21"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -2437,7 +2399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B1198"/>
+  <dimension ref="A1:B1145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7920,230 +7882,8 @@
     <row r="1175" ht="15" customHeight="1"/>
     <row r="1176" ht="15" customHeight="1"/>
     <row r="1177" ht="15" customHeight="1"/>
-    <row r="1180" ht="28" customHeight="1">
-      <c r="A1180" s="20" t="inlineStr">
-        <is>
-          <t>BUG-021   [Page] The page loads jQuery 1.11.1, and that line is no longer supported</t>
-        </is>
-      </c>
-      <c r="B1180" s="21" t="n"/>
-    </row>
-    <row r="1181" ht="24" customHeight="1">
-      <c r="A1181" s="4" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1181" s="5" t="inlineStr">
-        <is>
-          <t>BUG-021</t>
-        </is>
-      </c>
-    </row>
-    <row r="1182" ht="24" customHeight="1">
-      <c r="A1182" s="4" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1182" s="5" t="inlineStr">
-        <is>
-          <t>[Page] The page loads jQuery 1.11.1, and that line is no longer supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="1183" ht="24" customHeight="1">
-      <c r="A1183" s="4" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1183" s="5" t="inlineStr">
-        <is>
-          <t>Test drive registration</t>
-        </is>
-      </c>
-    </row>
-    <row r="1184" ht="24" customHeight="1">
-      <c r="A1184" s="4" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B1184" s="5" t="inlineStr">
-        <is>
-          <t>Third-party libraries</t>
-        </is>
-      </c>
-    </row>
-    <row r="1185" ht="24" customHeight="1">
-      <c r="A1185" s="4" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="B1185" s="22" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-    </row>
-    <row r="1186" ht="24" customHeight="1">
-      <c r="A1186" s="4" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="B1186" s="5" t="inlineStr"/>
-    </row>
-    <row r="1187" ht="24" customHeight="1">
-      <c r="A1187" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B1187" s="5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="1188" ht="24" customHeight="1">
-      <c r="A1188" s="4" t="inlineStr">
-        <is>
-          <t>Author</t>
-        </is>
-      </c>
-      <c r="B1188" s="5" t="inlineStr">
-        <is>
-          <t>Pavel</t>
-        </is>
-      </c>
-    </row>
-    <row r="1189" ht="24" customHeight="1">
-      <c r="A1189" s="4" t="inlineStr">
-        <is>
-          <t>Date found</t>
-        </is>
-      </c>
-      <c r="B1189" s="5" t="inlineStr">
-        <is>
-          <t>20 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="1190" ht="40" customHeight="1">
-      <c r="A1190" s="4" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-      <c r="B1190" s="5" t="inlineStr">
-        <is>
-          <t>OS: Linux, desktop. Browser: Google Chrome 148.0.7778.96. Window: 1440×900, zoom 100%. URL: https://testdrive.andersenlab.com/. Page build: Last-Modified 23 Apr 2026 13:11:09 GMT. Desktop only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1191" ht="24" customHeight="1">
-      <c r="A1191" s="4" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="B1191" s="5" t="inlineStr">
-        <is>
-          <t>The page has finished loading.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1192" ht="24" customHeight="1">
-      <c r="A1192" s="4" t="inlineStr">
-        <is>
-          <t>Test data</t>
-        </is>
-      </c>
-      <c r="B1192" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="1193" ht="56" customHeight="1">
-      <c r="A1193" s="4" t="inlineStr">
-        <is>
-          <t>Steps to reproduce</t>
-        </is>
-      </c>
-      <c r="B1193" s="5" t="inlineStr">
-        <is>
-          <t>1. Open https://testdrive.andersenlab.com/.
-2. In the browser console, evaluate jQuery.fn.jquery.
-3. In the page source, find the address of the jQuery script.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1194" ht="24" customHeight="1">
-      <c r="A1194" s="4" t="inlineStr">
-        <is>
-          <t>Expected result</t>
-        </is>
-      </c>
-      <c r="B1194" s="5" t="inlineStr">
-        <is>
-          <t>The page uses a supported jQuery release.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1195" ht="56" customHeight="1">
-      <c r="A1195" s="4" t="inlineStr">
-        <is>
-          <t>Actual result</t>
-        </is>
-      </c>
-      <c r="B1195" s="5" t="inlineStr">
-        <is>
-          <t>jQuery.fn.jquery returns "1.11.1". The script is loaded from https://ajax.googleapis.com/ajax/libs/jquery/1/jquery.min.js. Published advisories for the 1.x line include CVE-2015-9251, CVE-2019-11358, CVE-2020-11022, and CVE-2020-11023. The console had no messages when the page loaded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1196" ht="24" customHeight="1">
-      <c r="A1196" s="4" t="inlineStr">
-        <is>
-          <t>Reproducibility</t>
-        </is>
-      </c>
-      <c r="B1196" s="5" t="inlineStr">
-        <is>
-          <t>Always (5/5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1197" ht="24" customHeight="1">
-      <c r="A1197" s="4" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="B1197" s="5" t="inlineStr">
-        <is>
-          <t>No screenshot: the defect is not visible in an image. The check is described in the comment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1198" ht="40" customHeight="1">
-      <c r="A1198" s="4" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="B1198" s="5" t="inlineStr">
-        <is>
-          <t>A first name containing &lt;script&gt;alert(1)&lt;/script&gt; was shown as text and did not run. No working exploit on the form was demonstrated. The defect is the library version.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A530:B530"/>
     <mergeCell ref="A300:B300"/>
@@ -8156,7 +7896,6 @@
     <mergeCell ref="A706:B706"/>
     <mergeCell ref="A1126:B1126"/>
     <mergeCell ref="A354:B354"/>
-    <mergeCell ref="A1180:B1180"/>
     <mergeCell ref="A652:B652"/>
     <mergeCell ref="A246:B246"/>
     <mergeCell ref="A84:B84"/>
@@ -8168,7 +7907,7 @@
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="20" manualBreakCount="20">
+  <rowBreaks count="19" manualBreakCount="19">
     <brk id="29" min="0" max="16383" man="1"/>
     <brk id="83" min="0" max="16383" man="1"/>
     <brk id="137" min="0" max="16383" man="1"/>
@@ -8188,7 +7927,6 @@
     <brk id="1051" min="0" max="16383" man="1"/>
     <brk id="1071" min="0" max="16383" man="1"/>
     <brk id="1125" min="0" max="16383" man="1"/>
-    <brk id="1179" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/bug-reports/Bug_Report_Test_Drive.xlsx
+++ b/bug-reports/Bug_Report_Test_Drive.xlsx
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F9" s="18" t="inlineStr">
         <is>
-          <t>Step 3. Contact details and confirmation</t>
+          <t>Step 3. Contact details</t>
         </is>
       </c>
       <c r="G9" s="18" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>Step 3. Contact details and confirmation</t>
+          <t>Step 3. Contact details</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F11" s="18" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Step 3. Contact details</t>
         </is>
       </c>
       <c r="G11" s="18" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F12" s="18" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Step 3. Contact details</t>
         </is>
       </c>
       <c r="G12" s="18" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Step 3. Contact details</t>
         </is>
       </c>
       <c r="G13" s="18" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="F18" s="18" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Step 3. Contact details</t>
         </is>
       </c>
       <c r="G18" s="18" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="B358" s="5" t="inlineStr">
         <is>
-          <t>Step 3. Contact details and confirmation</t>
+          <t>Step 3. Contact details</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="B480" s="5" t="inlineStr">
         <is>
-          <t>Step 3. Contact details and confirmation</t>
+          <t>Step 3. Contact details</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B534" s="5" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Step 3. Contact details</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B656" s="5" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Step 3. Contact details</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="B710" s="5" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Step 3. Contact details</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="B1002" s="5" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Step 3. Contact details</t>
         </is>
       </c>
     </row>

--- a/bug-reports/Bug_Report_Test_Drive.xlsx
+++ b/bug-reports/Bug_Report_Test_Drive.xlsx
@@ -11,13 +11,10 @@
     <sheet name="Register" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Bug reports" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Improvements" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Passed checks" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Register'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Register'!$A$1:$H$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Register'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Passed checks'!$A$1:$C$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Passed checks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,14 +90,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="13"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00196F3D"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -135,21 +126,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D5D8DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5B7B1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAD7A0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
   </fills>
@@ -212,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -240,15 +216,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -296,9 +263,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -953,31 +917,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>1145</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7239000" cy="4524375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1270,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:D29"/>
+  <dimension ref="B2:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1467,98 +1406,35 @@
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Priority — fix order</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>When to fix it</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Before this module is placed on the dealer website.</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>In this same release. A request can still be sent, but the customer sees the wrong data or cannot correct it.</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>After the High and Medium defects.</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
           <t>Result</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>Defects: 20. Critical — 1, Major — 11, Minor — 7, Trivial — 1. Priority is left blank in every report. Improvements kept out of the defect list: 2. Every defect reproduces always, 5 out of 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Defects: 19. Critical — 1, Major — 11, Minor — 6, Trivial — 1. Improvements kept out of the defect list: 2. Every defect reproduces always, 5 out of 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1"/>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="15">
+    <mergeCell ref="B3:D3"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B22:D23"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B28:D29"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1571,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1627,14 +1503,14 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>BUG-001</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t>[Page] The browser tab has no page title</t>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>The browser window has no page title</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
@@ -1642,35 +1518,35 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D2" s="19" t="inlineStr"/>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr"/>
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
-        <is>
-          <t>Page shell</t>
-        </is>
-      </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>Browser window</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H2" s="18" t="inlineStr">
+      <c r="H2" s="15" t="inlineStr">
         <is>
           <t>browser-tab-crop.png</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>BUG-002</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>[Choose the model] "Cayenne 400" is shown as a Mercedes-Benz hatchback</t>
         </is>
@@ -1680,35 +1556,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr"/>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr"/>
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>Step 1. Choose the model</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>model-cayenne-400.png</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>BUG-003</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>[GLC 250D 4MATIC] The Engine list contains OutOfMemoryError</t>
         </is>
@@ -1718,35 +1594,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr"/>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr"/>
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>Step 2. Technical characteristics</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>glc-oom-selected.png</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>BUG-004</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>[GLC 250D 4MATIC] Leaving the engine unchanged submits Petrol 2.2</t>
         </is>
@@ -1756,35 +1632,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr"/>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr"/>
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Step 2. Technical characteristics</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>glc-default-petrol-confirm.png</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>BUG-005</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>[Confirmation] Engine OutOfMemoryError is shown as {transmission}</t>
         </is>
@@ -1794,37 +1670,37 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr"/>
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Step 4. Confirm the data</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>confirm-transmission-placeholder.png</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>BUG-006</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>[Wizard] Step numbers run 1, 2, 4, 5</t>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Step numbers run 1, 2, 4, 5</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1832,37 +1708,37 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr"/>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr"/>
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>Wizard heading</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Step 3, 4</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>contact-step-numbered-4.png</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>BUG-007</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>[Wizard] There is no way back to the previous step</t>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>There is no way back to the previous step</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1870,35 +1746,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr"/>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr"/>
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>Wizard navigation</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Application navigation</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>browser-back-leaves-wizard.png</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>BUG-008</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>[Contacts] An empty registration can be booked, and the summary shows field templates</t>
         </is>
@@ -1908,35 +1784,35 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr"/>
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Step 3. Contact details</t>
         </is>
       </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>confirm-empty-placeholders.png</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>BUG-009</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>[Contacts] Spaces-only values are accepted and the name disappears from the summary</t>
         </is>
@@ -1946,35 +1822,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr"/>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr"/>
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Step 3. Contact details</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t>confirm-whitespace.png</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>BUG-010</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>[Contacts] Age accepts a negative number</t>
         </is>
@@ -1984,35 +1860,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr"/>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr"/>
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Step 3. Contact details</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>confirm-invalid-age-phone.png</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>BUG-011</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>[Contacts] The phone field accepts letters</t>
         </is>
@@ -2022,35 +1898,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr"/>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr"/>
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Step 3. Contact details</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>confirm-invalid-age-phone.png</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>BUG-012</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>[Contacts] Name fields accept digits and symbols</t>
         </is>
@@ -2060,35 +1936,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr"/>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr"/>
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>Step 3. Contact details</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>confirm-symbols.png</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>BUG-013</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>[Confirmation] A long name with no spaces runs off the page</t>
         </is>
@@ -2098,35 +1974,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr"/>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr"/>
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>Step 4. Confirm the data</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>confirm-long-name-overflow.png</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>BUG-014</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>[Confirmation] The configuration line has a space before the comma</t>
         </is>
@@ -2136,37 +2012,37 @@
           <t>Trivial</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr"/>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr"/>
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>Step 4. Confirm the data</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t>confirm-valid-punctuation.png</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>BUG-015</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>[Copy] Labels and sentences in the wizard contain grammar errors</t>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>[Copy] Labels and sentences contain grammar errors</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -2174,35 +2050,35 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr"/>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr"/>
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>Interface copy</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>step2-transmissions-label.png</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>BUG-016</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>[Choose the model] Fast clicks on the arrow stack several cars on top of each other</t>
         </is>
@@ -2212,35 +2088,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr"/>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr"/>
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>Step 1. Choose the model</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H17" s="18" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>carousel-rapid-clicks.png</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>BUG-017</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>[Contacts] The field caption is not tied to the field and does not focus it</t>
         </is>
@@ -2250,35 +2126,35 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr"/>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr"/>
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>Step 3. Contact details</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>contact-step-numbered-4.png</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>BUG-018</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>[Choose the model] The carousel arrows cannot be operated from the keyboard</t>
         </is>
@@ -2288,37 +2164,37 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr"/>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr"/>
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Step 1. Choose the model</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H19" s="18" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>BUG-019</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>[Page] Images have no text alternative, and the page language is not set</t>
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>BUG-020</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>[Thank you] After Book, the screen does not show what was booked</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -2326,68 +2202,30 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr"/>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr"/>
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>Page shell</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Step 5. Thank-you screen</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
         <is>
           <t>Always (5/5)</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>model-s500.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>BUG-020</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>[Thank you] After Book, the screen does not show what was booked</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr"/>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>Thank-you screen</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>Always (5/5)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
+      <c r="H20" s="15" t="inlineStr">
         <is>
           <t>thank-you.png</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H21"/>
+  <autoFilter ref="A1:H20"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -2399,7 +2237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B1145"/>
+  <dimension ref="A1:B1091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2407,12 +2245,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>BUG-001   [Page] The browser tab has no page title</t>
-        </is>
-      </c>
-      <c r="B1" s="21" t="n"/>
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>BUG-001   The browser window has no page title</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -2434,7 +2272,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>[Page] The browser tab has no page title</t>
+          <t>The browser window has no page title</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2296,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Page shell</t>
+          <t>Browser window</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2306,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -2628,12 +2466,12 @@
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>browser-tab-crop.png</t>
         </is>
@@ -2647,12 +2485,12 @@
     <row r="26" ht="15" customHeight="1"/>
     <row r="27" ht="15" customHeight="1"/>
     <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>BUG-002   [Choose the model] "Cayenne 400" is shown as a Mercedes-Benz hatchback</t>
         </is>
       </c>
-      <c r="B30" s="21" t="n"/>
+      <c r="B30" s="18" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -2708,7 +2546,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B35" s="26" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -2870,12 +2708,12 @@
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="23" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B49" s="24" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>model-cayenne-400.png</t>
         </is>
@@ -2914,12 +2752,12 @@
     <row r="80" ht="15" customHeight="1"/>
     <row r="81" ht="15" customHeight="1"/>
     <row r="84" ht="28" customHeight="1">
-      <c r="A84" s="25" t="inlineStr">
+      <c r="A84" s="22" t="inlineStr">
         <is>
           <t>BUG-003   [GLC 250D 4MATIC] The Engine list contains OutOfMemoryError</t>
         </is>
       </c>
-      <c r="B84" s="21" t="n"/>
+      <c r="B84" s="18" t="n"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -2975,7 +2813,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B89" s="26" t="inlineStr">
+      <c r="B89" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -3136,12 +2974,12 @@
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="23" t="inlineStr">
+      <c r="A103" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B103" s="24" t="inlineStr">
+      <c r="B103" s="21" t="inlineStr">
         <is>
           <t>glc-oom-selected.png</t>
         </is>
@@ -3180,12 +3018,12 @@
     <row r="134" ht="15" customHeight="1"/>
     <row r="135" ht="15" customHeight="1"/>
     <row r="138" ht="28" customHeight="1">
-      <c r="A138" s="25" t="inlineStr">
+      <c r="A138" s="22" t="inlineStr">
         <is>
           <t>BUG-004   [GLC 250D 4MATIC] Leaving the engine unchanged submits Petrol 2.2</t>
         </is>
       </c>
-      <c r="B138" s="21" t="n"/>
+      <c r="B138" s="18" t="n"/>
     </row>
     <row r="139" ht="24" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
@@ -3241,7 +3079,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B143" s="26" t="inlineStr">
+      <c r="B143" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -3404,12 +3242,12 @@
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
-      <c r="A157" s="23" t="inlineStr">
+      <c r="A157" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B157" s="24" t="inlineStr">
+      <c r="B157" s="21" t="inlineStr">
         <is>
           <t>glc-default-petrol-confirm.png</t>
         </is>
@@ -3448,12 +3286,12 @@
     <row r="188" ht="15" customHeight="1"/>
     <row r="189" ht="15" customHeight="1"/>
     <row r="192" ht="28" customHeight="1">
-      <c r="A192" s="25" t="inlineStr">
+      <c r="A192" s="22" t="inlineStr">
         <is>
           <t>BUG-005   [Confirmation] Engine OutOfMemoryError is shown as {transmission}</t>
         </is>
       </c>
-      <c r="B192" s="21" t="n"/>
+      <c r="B192" s="18" t="n"/>
     </row>
     <row r="193" ht="24" customHeight="1">
       <c r="A193" s="4" t="inlineStr">
@@ -3509,7 +3347,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B197" s="26" t="inlineStr">
+      <c r="B197" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -3673,12 +3511,12 @@
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
-      <c r="A211" s="23" t="inlineStr">
+      <c r="A211" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B211" s="24" t="inlineStr">
+      <c r="B211" s="21" t="inlineStr">
         <is>
           <t>confirm-transmission-placeholder.png</t>
         </is>
@@ -3717,12 +3555,12 @@
     <row r="242" ht="15" customHeight="1"/>
     <row r="243" ht="15" customHeight="1"/>
     <row r="246" ht="28" customHeight="1">
-      <c r="A246" s="20" t="inlineStr">
-        <is>
-          <t>BUG-006   [Wizard] Step numbers run 1, 2, 4, 5</t>
-        </is>
-      </c>
-      <c r="B246" s="21" t="n"/>
+      <c r="A246" s="17" t="inlineStr">
+        <is>
+          <t>BUG-006   Step numbers run 1, 2, 4, 5</t>
+        </is>
+      </c>
+      <c r="B246" s="18" t="n"/>
     </row>
     <row r="247" ht="24" customHeight="1">
       <c r="A247" s="4" t="inlineStr">
@@ -3744,7 +3582,7 @@
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>[Wizard] Step numbers run 1, 2, 4, 5</t>
+          <t>Step numbers run 1, 2, 4, 5</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3606,7 @@
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>Wizard heading</t>
+          <t>Step 3, 4</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3616,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B251" s="22" t="inlineStr">
+      <c r="B251" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -3940,12 +3778,12 @@
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
-      <c r="A265" s="23" t="inlineStr">
+      <c r="A265" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B265" s="24" t="inlineStr">
+      <c r="B265" s="21" t="inlineStr">
         <is>
           <t>contact-step-numbered-4.png</t>
         </is>
@@ -3984,12 +3822,12 @@
     <row r="296" ht="15" customHeight="1"/>
     <row r="297" ht="15" customHeight="1"/>
     <row r="300" ht="28" customHeight="1">
-      <c r="A300" s="25" t="inlineStr">
-        <is>
-          <t>BUG-007   [Wizard] There is no way back to the previous step</t>
-        </is>
-      </c>
-      <c r="B300" s="21" t="n"/>
+      <c r="A300" s="22" t="inlineStr">
+        <is>
+          <t>BUG-007   There is no way back to the previous step</t>
+        </is>
+      </c>
+      <c r="B300" s="18" t="n"/>
     </row>
     <row r="301" ht="24" customHeight="1">
       <c r="A301" s="4" t="inlineStr">
@@ -4011,7 +3849,7 @@
       </c>
       <c r="B302" s="5" t="inlineStr">
         <is>
-          <t>[Wizard] There is no way back to the previous step</t>
+          <t>There is no way back to the previous step</t>
         </is>
       </c>
     </row>
@@ -4035,7 +3873,7 @@
       </c>
       <c r="B304" s="5" t="inlineStr">
         <is>
-          <t>Wizard navigation</t>
+          <t>Application navigation</t>
         </is>
       </c>
     </row>
@@ -4045,7 +3883,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B305" s="26" t="inlineStr">
+      <c r="B305" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -4154,7 +3992,7 @@
       </c>
       <c r="B314" s="5" t="inlineStr">
         <is>
-          <t>From the second step onward there is a way back, and the choice already made is kept. The browser Back button opens the previous wizard step.</t>
+          <t>From the second step onward there is a way back, and the choice already made is kept. The browser Back button opens the previous application step.</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4004,7 @@
       </c>
       <c r="B315" s="5" t="inlineStr">
         <is>
-          <t>The wizard screens have only Continue. The confirmation screen has only Book. There is no back control. The browser Back button leaves testdrive.andersenlab.com and opens the previous site. In this check it opened https://example.com/. The model, engine, and contact details cannot be corrected.</t>
+          <t>The application screens have only Continue. The confirmation screen has only Book. There is no back control. The browser Back button leaves testdrive.andersenlab.com and opens the previous site. In this check it opened https://example.com/. The model, engine, and contact details cannot be corrected.</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4045,12 @@
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
-      <c r="A319" s="23" t="inlineStr">
+      <c r="A319" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B319" s="24" t="inlineStr">
+      <c r="B319" s="21" t="inlineStr">
         <is>
           <t>browser-back-leaves-wizard.png</t>
         </is>
@@ -4251,12 +4089,12 @@
     <row r="350" ht="15" customHeight="1"/>
     <row r="351" ht="15" customHeight="1"/>
     <row r="354" ht="28" customHeight="1">
-      <c r="A354" s="27" t="inlineStr">
+      <c r="A354" s="24" t="inlineStr">
         <is>
           <t>BUG-008   [Contacts] An empty registration can be booked, and the summary shows field templates</t>
         </is>
       </c>
-      <c r="B354" s="21" t="n"/>
+      <c r="B354" s="18" t="n"/>
     </row>
     <row r="355" ht="24" customHeight="1">
       <c r="A355" s="4" t="inlineStr">
@@ -4312,7 +4150,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B359" s="28" t="inlineStr">
+      <c r="B359" s="25" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -4433,7 +4271,7 @@
       </c>
       <c r="B369" s="5" t="inlineStr">
         <is>
-          <t>Continue opens the confirmation. The screen says: "Your name is {lastName} {firstName} {middleName} and you are {age} years old." and "Phone number we can reach you at {phone}." There is no error message. Book finishes the wizard. The next screen shows "Thank you for booking the test drive!" and "Our managers will contact you within next 12 hours."</t>
+          <t>Continue opens the confirmation. The screen says: "Your name is {lastName} {firstName} {middleName} and you are {age} years old." and "Phone number we can reach you at {phone}." There is no error message. Book finishes the application. The next screen shows "Thank you for booking the test drive!" and "Our managers will contact you within next 12 hours."</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4312,12 @@
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
-      <c r="A373" s="23" t="inlineStr">
+      <c r="A373" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B373" s="24" t="inlineStr">
+      <c r="B373" s="21" t="inlineStr">
         <is>
           <t>confirm-empty-placeholders.png</t>
         </is>
@@ -4518,12 +4356,12 @@
     <row r="404" ht="15" customHeight="1"/>
     <row r="405" ht="15" customHeight="1"/>
     <row r="407" ht="18" customHeight="1">
-      <c r="A407" s="23" t="inlineStr">
+      <c r="A407" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B407" s="24" t="inlineStr">
+      <c r="B407" s="21" t="inlineStr">
         <is>
           <t>empty-booked-thanks.png</t>
         </is>
@@ -4562,12 +4400,12 @@
     <row r="438" ht="15" customHeight="1"/>
     <row r="439" ht="15" customHeight="1"/>
     <row r="441" ht="18" customHeight="1">
-      <c r="A441" s="23" t="inlineStr">
+      <c r="A441" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B441" s="24" t="inlineStr">
+      <c r="B441" s="21" t="inlineStr">
         <is>
           <t>confirm-missing-middle-name.png</t>
         </is>
@@ -4606,12 +4444,12 @@
     <row r="472" ht="15" customHeight="1"/>
     <row r="473" ht="15" customHeight="1"/>
     <row r="476" ht="28" customHeight="1">
-      <c r="A476" s="25" t="inlineStr">
+      <c r="A476" s="22" t="inlineStr">
         <is>
           <t>BUG-009   [Contacts] Spaces-only values are accepted and the name disappears from the summary</t>
         </is>
       </c>
-      <c r="B476" s="21" t="n"/>
+      <c r="B476" s="18" t="n"/>
     </row>
     <row r="477" ht="24" customHeight="1">
       <c r="A477" s="4" t="inlineStr">
@@ -4667,7 +4505,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B481" s="26" t="inlineStr">
+      <c r="B481" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -4828,12 +4666,12 @@
       </c>
     </row>
     <row r="495" ht="18" customHeight="1">
-      <c r="A495" s="23" t="inlineStr">
+      <c r="A495" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B495" s="24" t="inlineStr">
+      <c r="B495" s="21" t="inlineStr">
         <is>
           <t>confirm-whitespace.png</t>
         </is>
@@ -4872,12 +4710,12 @@
     <row r="526" ht="15" customHeight="1"/>
     <row r="527" ht="15" customHeight="1"/>
     <row r="530" ht="28" customHeight="1">
-      <c r="A530" s="25" t="inlineStr">
+      <c r="A530" s="22" t="inlineStr">
         <is>
           <t>BUG-010   [Contacts] Age accepts a negative number</t>
         </is>
       </c>
-      <c r="B530" s="21" t="n"/>
+      <c r="B530" s="18" t="n"/>
     </row>
     <row r="531" ht="24" customHeight="1">
       <c r="A531" s="4" t="inlineStr">
@@ -4933,7 +4771,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B535" s="26" t="inlineStr">
+      <c r="B535" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -5094,12 +4932,12 @@
       </c>
     </row>
     <row r="549" ht="18" customHeight="1">
-      <c r="A549" s="23" t="inlineStr">
+      <c r="A549" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B549" s="24" t="inlineStr">
+      <c r="B549" s="21" t="inlineStr">
         <is>
           <t>confirm-invalid-age-phone.png</t>
         </is>
@@ -5138,12 +4976,12 @@
     <row r="580" ht="15" customHeight="1"/>
     <row r="581" ht="15" customHeight="1"/>
     <row r="583" ht="18" customHeight="1">
-      <c r="A583" s="23" t="inlineStr">
+      <c r="A583" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B583" s="24" t="inlineStr">
+      <c r="B583" s="21" t="inlineStr">
         <is>
           <t>confirm-age-text.png</t>
         </is>
@@ -5182,12 +5020,12 @@
     <row r="614" ht="15" customHeight="1"/>
     <row r="615" ht="15" customHeight="1"/>
     <row r="617" ht="18" customHeight="1">
-      <c r="A617" s="23" t="inlineStr">
+      <c r="A617" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B617" s="24" t="inlineStr">
+      <c r="B617" s="21" t="inlineStr">
         <is>
           <t>confirm-age-15.png</t>
         </is>
@@ -5226,12 +5064,12 @@
     <row r="648" ht="15" customHeight="1"/>
     <row r="649" ht="15" customHeight="1"/>
     <row r="652" ht="28" customHeight="1">
-      <c r="A652" s="25" t="inlineStr">
+      <c r="A652" s="22" t="inlineStr">
         <is>
           <t>BUG-011   [Contacts] The phone field accepts letters</t>
         </is>
       </c>
-      <c r="B652" s="21" t="n"/>
+      <c r="B652" s="18" t="n"/>
     </row>
     <row r="653" ht="24" customHeight="1">
       <c r="A653" s="4" t="inlineStr">
@@ -5287,7 +5125,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B657" s="26" t="inlineStr">
+      <c r="B657" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -5449,12 +5287,12 @@
       </c>
     </row>
     <row r="671" ht="18" customHeight="1">
-      <c r="A671" s="23" t="inlineStr">
+      <c r="A671" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B671" s="24" t="inlineStr">
+      <c r="B671" s="21" t="inlineStr">
         <is>
           <t>confirm-invalid-age-phone.png</t>
         </is>
@@ -5493,12 +5331,12 @@
     <row r="702" ht="15" customHeight="1"/>
     <row r="703" ht="15" customHeight="1"/>
     <row r="706" ht="28" customHeight="1">
-      <c r="A706" s="25" t="inlineStr">
+      <c r="A706" s="22" t="inlineStr">
         <is>
           <t>BUG-012   [Contacts] Name fields accept digits and symbols</t>
         </is>
       </c>
-      <c r="B706" s="21" t="n"/>
+      <c r="B706" s="18" t="n"/>
     </row>
     <row r="707" ht="24" customHeight="1">
       <c r="A707" s="4" t="inlineStr">
@@ -5554,7 +5392,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B711" s="26" t="inlineStr">
+      <c r="B711" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -5715,12 +5553,12 @@
       </c>
     </row>
     <row r="725" ht="18" customHeight="1">
-      <c r="A725" s="23" t="inlineStr">
+      <c r="A725" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B725" s="24" t="inlineStr">
+      <c r="B725" s="21" t="inlineStr">
         <is>
           <t>confirm-symbols.png</t>
         </is>
@@ -5759,12 +5597,12 @@
     <row r="756" ht="15" customHeight="1"/>
     <row r="757" ht="15" customHeight="1"/>
     <row r="760" ht="28" customHeight="1">
-      <c r="A760" s="25" t="inlineStr">
+      <c r="A760" s="22" t="inlineStr">
         <is>
           <t>BUG-013   [Confirmation] A long name with no spaces runs off the page</t>
         </is>
       </c>
-      <c r="B760" s="21" t="n"/>
+      <c r="B760" s="18" t="n"/>
     </row>
     <row r="761" ht="24" customHeight="1">
       <c r="A761" s="4" t="inlineStr">
@@ -5820,7 +5658,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B765" s="26" t="inlineStr">
+      <c r="B765" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -5981,12 +5819,12 @@
       </c>
     </row>
     <row r="779" ht="18" customHeight="1">
-      <c r="A779" s="23" t="inlineStr">
+      <c r="A779" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B779" s="24" t="inlineStr">
+      <c r="B779" s="21" t="inlineStr">
         <is>
           <t>confirm-long-name-overflow.png</t>
         </is>
@@ -6013,12 +5851,12 @@
     <row r="798" ht="15" customHeight="1"/>
     <row r="799" ht="15" customHeight="1"/>
     <row r="802" ht="28" customHeight="1">
-      <c r="A802" s="29" t="inlineStr">
+      <c r="A802" s="26" t="inlineStr">
         <is>
           <t>BUG-014   [Confirmation] The configuration line has a space before the comma</t>
         </is>
       </c>
-      <c r="B802" s="21" t="n"/>
+      <c r="B802" s="18" t="n"/>
     </row>
     <row r="803" ht="24" customHeight="1">
       <c r="A803" s="4" t="inlineStr">
@@ -6074,7 +5912,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B807" s="30" t="inlineStr">
+      <c r="B807" s="27" t="inlineStr">
         <is>
           <t>Trivial</t>
         </is>
@@ -6234,12 +6072,12 @@
       </c>
     </row>
     <row r="821" ht="18" customHeight="1">
-      <c r="A821" s="23" t="inlineStr">
+      <c r="A821" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B821" s="24" t="inlineStr">
+      <c r="B821" s="21" t="inlineStr">
         <is>
           <t>confirm-valid-punctuation.png</t>
         </is>
@@ -6278,12 +6116,12 @@
     <row r="852" ht="15" customHeight="1"/>
     <row r="853" ht="15" customHeight="1"/>
     <row r="856" ht="28" customHeight="1">
-      <c r="A856" s="20" t="inlineStr">
-        <is>
-          <t>BUG-015   [Copy] Labels and sentences in the wizard contain grammar errors</t>
-        </is>
-      </c>
-      <c r="B856" s="21" t="n"/>
+      <c r="A856" s="17" t="inlineStr">
+        <is>
+          <t>BUG-015   [Copy] Labels and sentences contain grammar errors</t>
+        </is>
+      </c>
+      <c r="B856" s="18" t="n"/>
     </row>
     <row r="857" ht="24" customHeight="1">
       <c r="A857" s="4" t="inlineStr">
@@ -6305,7 +6143,7 @@
       </c>
       <c r="B858" s="5" t="inlineStr">
         <is>
-          <t>[Copy] Labels and sentences in the wizard contain grammar errors</t>
+          <t>[Copy] Labels and sentences contain grammar errors</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6177,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B861" s="22" t="inlineStr">
+      <c r="B861" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -6409,7 +6247,7 @@
       </c>
       <c r="B867" s="5" t="inlineStr">
         <is>
-          <t>The wizard can be completed through the thank-you screen.</t>
+          <t>The application can be completed through the thank-you screen.</t>
         </is>
       </c>
     </row>
@@ -6510,12 +6348,12 @@
       </c>
     </row>
     <row r="875" ht="18" customHeight="1">
-      <c r="A875" s="23" t="inlineStr">
+      <c r="A875" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B875" s="24" t="inlineStr">
+      <c r="B875" s="21" t="inlineStr">
         <is>
           <t>step2-transmissions-label.png</t>
         </is>
@@ -6554,12 +6392,12 @@
     <row r="906" ht="15" customHeight="1"/>
     <row r="907" ht="15" customHeight="1"/>
     <row r="909" ht="18" customHeight="1">
-      <c r="A909" s="23" t="inlineStr">
+      <c r="A909" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B909" s="24" t="inlineStr">
+      <c r="B909" s="21" t="inlineStr">
         <is>
           <t>thank-you.png</t>
         </is>
@@ -6598,12 +6436,12 @@
     <row r="940" ht="15" customHeight="1"/>
     <row r="941" ht="15" customHeight="1"/>
     <row r="944" ht="28" customHeight="1">
-      <c r="A944" s="25" t="inlineStr">
+      <c r="A944" s="22" t="inlineStr">
         <is>
           <t>BUG-016   [Choose the model] Fast clicks on the arrow stack several cars on top of each other</t>
         </is>
       </c>
-      <c r="B944" s="21" t="n"/>
+      <c r="B944" s="18" t="n"/>
     </row>
     <row r="945" ht="24" customHeight="1">
       <c r="A945" s="4" t="inlineStr">
@@ -6659,7 +6497,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B949" s="26" t="inlineStr">
+      <c r="B949" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -6779,7 +6617,7 @@
       </c>
       <c r="B959" s="5" t="inlineStr">
         <is>
-          <t>Until the animation ends, several cars are on screen at once, at different opacity. The caption is barely readable. A second car is drawn lower down, and Continue sits on top of it. Continue still advances the wizard during this state. A few seconds later one car remains: after six clicks it is GLC 250D 4MATIC.</t>
+          <t>Until the animation ends, several cars are on screen at once, at different opacity. The caption is barely readable. A second car is drawn lower down, and Continue sits on top of it. Continue still advances the application during this state. A few seconds later one car remains: after six clicks it is GLC 250D 4MATIC.</t>
         </is>
       </c>
     </row>
@@ -6820,12 +6658,12 @@
       </c>
     </row>
     <row r="963" ht="18" customHeight="1">
-      <c r="A963" s="23" t="inlineStr">
+      <c r="A963" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B963" s="24" t="inlineStr">
+      <c r="B963" s="21" t="inlineStr">
         <is>
           <t>carousel-rapid-clicks.png</t>
         </is>
@@ -6864,12 +6702,12 @@
     <row r="994" ht="15" customHeight="1"/>
     <row r="995" ht="15" customHeight="1"/>
     <row r="998" ht="28" customHeight="1">
-      <c r="A998" s="20" t="inlineStr">
+      <c r="A998" s="17" t="inlineStr">
         <is>
           <t>BUG-017   [Contacts] The field caption is not tied to the field and does not focus it</t>
         </is>
       </c>
-      <c r="B998" s="21" t="n"/>
+      <c r="B998" s="18" t="n"/>
     </row>
     <row r="999" ht="24" customHeight="1">
       <c r="A999" s="4" t="inlineStr">
@@ -6925,7 +6763,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B1003" s="22" t="inlineStr">
+      <c r="B1003" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7086,12 +6924,12 @@
       </c>
     </row>
     <row r="1017" ht="18" customHeight="1">
-      <c r="A1017" s="23" t="inlineStr">
+      <c r="A1017" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B1017" s="24" t="inlineStr">
+      <c r="B1017" s="21" t="inlineStr">
         <is>
           <t>contact-step-numbered-4.png</t>
         </is>
@@ -7130,12 +6968,12 @@
     <row r="1048" ht="15" customHeight="1"/>
     <row r="1049" ht="15" customHeight="1"/>
     <row r="1052" ht="28" customHeight="1">
-      <c r="A1052" s="20" t="inlineStr">
+      <c r="A1052" s="17" t="inlineStr">
         <is>
           <t>BUG-018   [Choose the model] The carousel arrows cannot be operated from the keyboard</t>
         </is>
       </c>
-      <c r="B1052" s="21" t="n"/>
+      <c r="B1052" s="18" t="n"/>
     </row>
     <row r="1053" ht="24" customHeight="1">
       <c r="A1053" s="4" t="inlineStr">
@@ -7191,7 +7029,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B1057" s="22" t="inlineStr">
+      <c r="B1057" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7352,12 +7190,12 @@
       </c>
     </row>
     <row r="1072" ht="28" customHeight="1">
-      <c r="A1072" s="20" t="inlineStr">
-        <is>
-          <t>BUG-019   [Page] Images have no text alternative, and the page language is not set</t>
-        </is>
-      </c>
-      <c r="B1072" s="21" t="n"/>
+      <c r="A1072" s="17" t="inlineStr">
+        <is>
+          <t>BUG-020   [Thank you] After Book, the screen does not show what was booked</t>
+        </is>
+      </c>
+      <c r="B1072" s="18" t="n"/>
     </row>
     <row r="1073" ht="24" customHeight="1">
       <c r="A1073" s="4" t="inlineStr">
@@ -7367,7 +7205,7 @@
       </c>
       <c r="B1073" s="5" t="inlineStr">
         <is>
-          <t>BUG-019</t>
+          <t>BUG-020</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7217,7 @@
       </c>
       <c r="B1074" s="5" t="inlineStr">
         <is>
-          <t>[Page] Images have no text alternative, and the page language is not set</t>
+          <t>[Thank you] After Book, the screen does not show what was booked</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7241,7 @@
       </c>
       <c r="B1076" s="5" t="inlineStr">
         <is>
-          <t>Page shell</t>
+          <t>Step 5. Thank-you screen</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7251,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="B1077" s="22" t="inlineStr">
+      <c r="B1077" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7483,7 +7321,7 @@
       </c>
       <c r="B1083" s="5" t="inlineStr">
         <is>
-          <t>The registration page is open.</t>
+          <t>The confirmation is open and shows a model and a phone number.</t>
         </is>
       </c>
     </row>
@@ -7495,11 +7333,11 @@
       </c>
       <c r="B1084" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="1085" ht="40" customHeight="1">
+          <t>Any model and phone already visible on the confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085" ht="56" customHeight="1">
       <c r="A1085" s="4" t="inlineStr">
         <is>
           <t>Steps to reproduce</t>
@@ -7507,12 +7345,13 @@
       </c>
       <c r="B1085" s="5" t="inlineStr">
         <is>
-          <t>1. Check the text alternative of the logo and of the four car photos.
-2. Check the language set on the root element of the page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1086" ht="40" customHeight="1">
+          <t>1. Click Book.
+2. Read the thank-you screen.
+3. Look for the model, the configuration, the phone, and an action to start another registration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086" ht="56" customHeight="1">
       <c r="A1086" s="4" t="inlineStr">
         <is>
           <t>Expected result</t>
@@ -7520,11 +7359,11 @@
       </c>
       <c r="B1086" s="5" t="inlineStr">
         <is>
-          <t>The logo and each photo have a text alternative that names them. The page language is set to English.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1087" ht="40" customHeight="1">
+          <t>The screen repeats the model, configuration, and phone from the previous step. There is a clear action to start another registration. A stored booking number is not expected: saving the customer is outside this module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087" ht="56" customHeight="1">
       <c r="A1087" s="4" t="inlineStr">
         <is>
           <t>Actual result</t>
@@ -7532,7 +7371,7 @@
       </c>
       <c r="B1087" s="5" t="inlineStr">
         <is>
-          <t>The alt attribute is missing on the logo and on all four car photos. The root html element has no lang attribute.</t>
+          <t>The screen shows only "Thank you for booking the test drive!" and "Our managers will contact you within next 12 hours." The model and the phone are not repeated. There is no button for a new registration. Starting again requires a manual reload.</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7395,7 @@
       </c>
       <c r="B1089" s="5" t="inlineStr">
         <is>
-          <t>model-s500.png</t>
+          <t>thank-you.png</t>
         </is>
       </c>
     </row>
@@ -7568,19 +7407,19 @@
       </c>
       <c r="B1090" s="5" t="inlineStr">
         <is>
-          <t>The empty browser-tab title is described separately in BUG-001.</t>
+          <t>The missing article in the 12-hours sentence is described in BUG-015.</t>
         </is>
       </c>
     </row>
     <row r="1091" ht="18" customHeight="1">
-      <c r="A1091" s="23" t="inlineStr">
+      <c r="A1091" s="20" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
       </c>
-      <c r="B1091" s="24" t="inlineStr">
-        <is>
-          <t>model-s500.png</t>
+      <c r="B1091" s="21" t="inlineStr">
+        <is>
+          <t>thank-you.png</t>
         </is>
       </c>
     </row>
@@ -7616,274 +7455,8 @@
     <row r="1121" ht="15" customHeight="1"/>
     <row r="1122" ht="15" customHeight="1"/>
     <row r="1123" ht="15" customHeight="1"/>
-    <row r="1126" ht="28" customHeight="1">
-      <c r="A1126" s="20" t="inlineStr">
-        <is>
-          <t>BUG-020   [Thank you] After Book, the screen does not show what was booked</t>
-        </is>
-      </c>
-      <c r="B1126" s="21" t="n"/>
-    </row>
-    <row r="1127" ht="24" customHeight="1">
-      <c r="A1127" s="4" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1127" s="5" t="inlineStr">
-        <is>
-          <t>BUG-020</t>
-        </is>
-      </c>
-    </row>
-    <row r="1128" ht="24" customHeight="1">
-      <c r="A1128" s="4" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1128" s="5" t="inlineStr">
-        <is>
-          <t>[Thank you] After Book, the screen does not show what was booked</t>
-        </is>
-      </c>
-    </row>
-    <row r="1129" ht="24" customHeight="1">
-      <c r="A1129" s="4" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1129" s="5" t="inlineStr">
-        <is>
-          <t>Test drive registration</t>
-        </is>
-      </c>
-    </row>
-    <row r="1130" ht="24" customHeight="1">
-      <c r="A1130" s="4" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B1130" s="5" t="inlineStr">
-        <is>
-          <t>Thank-you screen</t>
-        </is>
-      </c>
-    </row>
-    <row r="1131" ht="24" customHeight="1">
-      <c r="A1131" s="4" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="B1131" s="22" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-    </row>
-    <row r="1132" ht="24" customHeight="1">
-      <c r="A1132" s="4" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="B1132" s="5" t="inlineStr"/>
-    </row>
-    <row r="1133" ht="24" customHeight="1">
-      <c r="A1133" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B1133" s="5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="1134" ht="24" customHeight="1">
-      <c r="A1134" s="4" t="inlineStr">
-        <is>
-          <t>Author</t>
-        </is>
-      </c>
-      <c r="B1134" s="5" t="inlineStr">
-        <is>
-          <t>Pavel</t>
-        </is>
-      </c>
-    </row>
-    <row r="1135" ht="24" customHeight="1">
-      <c r="A1135" s="4" t="inlineStr">
-        <is>
-          <t>Date found</t>
-        </is>
-      </c>
-      <c r="B1135" s="5" t="inlineStr">
-        <is>
-          <t>20 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="1136" ht="40" customHeight="1">
-      <c r="A1136" s="4" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-      <c r="B1136" s="5" t="inlineStr">
-        <is>
-          <t>OS: Linux, desktop. Browser: Google Chrome 148.0.7778.96. Window: 1440×900, zoom 100%. URL: https://testdrive.andersenlab.com/. Page build: Last-Modified 23 Apr 2026 13:11:09 GMT. Desktop only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1137" ht="24" customHeight="1">
-      <c r="A1137" s="4" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="B1137" s="5" t="inlineStr">
-        <is>
-          <t>The confirmation is open and shows a model and a phone number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1138" ht="24" customHeight="1">
-      <c r="A1138" s="4" t="inlineStr">
-        <is>
-          <t>Test data</t>
-        </is>
-      </c>
-      <c r="B1138" s="5" t="inlineStr">
-        <is>
-          <t>Any model and phone already visible on the confirmation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1139" ht="56" customHeight="1">
-      <c r="A1139" s="4" t="inlineStr">
-        <is>
-          <t>Steps to reproduce</t>
-        </is>
-      </c>
-      <c r="B1139" s="5" t="inlineStr">
-        <is>
-          <t>1. Click Book.
-2. Read the thank-you screen.
-3. Look for the model, the configuration, the phone, and an action to start another registration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1140" ht="56" customHeight="1">
-      <c r="A1140" s="4" t="inlineStr">
-        <is>
-          <t>Expected result</t>
-        </is>
-      </c>
-      <c r="B1140" s="5" t="inlineStr">
-        <is>
-          <t>The screen repeats the model, configuration, and phone from the previous step. There is a clear action to start another registration. A stored booking number is not expected: saving the customer is outside this module.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1141" ht="56" customHeight="1">
-      <c r="A1141" s="4" t="inlineStr">
-        <is>
-          <t>Actual result</t>
-        </is>
-      </c>
-      <c r="B1141" s="5" t="inlineStr">
-        <is>
-          <t>The screen shows only "Thank you for booking the test drive!" and "Our managers will contact you within next 12 hours." The model and the phone are not repeated. There is no button for a new registration. Starting again requires a manual reload.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1142" ht="24" customHeight="1">
-      <c r="A1142" s="4" t="inlineStr">
-        <is>
-          <t>Reproducibility</t>
-        </is>
-      </c>
-      <c r="B1142" s="5" t="inlineStr">
-        <is>
-          <t>Always (5/5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1143" ht="24" customHeight="1">
-      <c r="A1143" s="4" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="B1143" s="5" t="inlineStr">
-        <is>
-          <t>thank-you.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="1144" ht="24" customHeight="1">
-      <c r="A1144" s="4" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="B1144" s="5" t="inlineStr">
-        <is>
-          <t>The missing article in the 12-hours sentence is described in BUG-015.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1145" ht="18" customHeight="1">
-      <c r="A1145" s="23" t="inlineStr">
-        <is>
-          <t>Screenshot</t>
-        </is>
-      </c>
-      <c r="B1145" s="24" t="inlineStr">
-        <is>
-          <t>thank-you.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="1146" ht="15" customHeight="1"/>
-    <row r="1147" ht="15" customHeight="1"/>
-    <row r="1148" ht="15" customHeight="1"/>
-    <row r="1149" ht="15" customHeight="1"/>
-    <row r="1150" ht="15" customHeight="1"/>
-    <row r="1151" ht="15" customHeight="1"/>
-    <row r="1152" ht="15" customHeight="1"/>
-    <row r="1153" ht="15" customHeight="1"/>
-    <row r="1154" ht="15" customHeight="1"/>
-    <row r="1155" ht="15" customHeight="1"/>
-    <row r="1156" ht="15" customHeight="1"/>
-    <row r="1157" ht="15" customHeight="1"/>
-    <row r="1158" ht="15" customHeight="1"/>
-    <row r="1159" ht="15" customHeight="1"/>
-    <row r="1160" ht="15" customHeight="1"/>
-    <row r="1161" ht="15" customHeight="1"/>
-    <row r="1162" ht="15" customHeight="1"/>
-    <row r="1163" ht="15" customHeight="1"/>
-    <row r="1164" ht="15" customHeight="1"/>
-    <row r="1165" ht="15" customHeight="1"/>
-    <row r="1166" ht="15" customHeight="1"/>
-    <row r="1167" ht="15" customHeight="1"/>
-    <row r="1168" ht="15" customHeight="1"/>
-    <row r="1169" ht="15" customHeight="1"/>
-    <row r="1170" ht="15" customHeight="1"/>
-    <row r="1171" ht="15" customHeight="1"/>
-    <row r="1172" ht="15" customHeight="1"/>
-    <row r="1173" ht="15" customHeight="1"/>
-    <row r="1174" ht="15" customHeight="1"/>
-    <row r="1175" ht="15" customHeight="1"/>
-    <row r="1176" ht="15" customHeight="1"/>
-    <row r="1177" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A530:B530"/>
     <mergeCell ref="A300:B300"/>
@@ -7894,7 +7467,6 @@
     <mergeCell ref="A998:B998"/>
     <mergeCell ref="A856:B856"/>
     <mergeCell ref="A706:B706"/>
-    <mergeCell ref="A1126:B1126"/>
     <mergeCell ref="A354:B354"/>
     <mergeCell ref="A652:B652"/>
     <mergeCell ref="A246:B246"/>
@@ -7907,7 +7479,7 @@
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="19" manualBreakCount="19">
+  <rowBreaks count="18" manualBreakCount="18">
     <brk id="29" min="0" max="16383" man="1"/>
     <brk id="83" min="0" max="16383" man="1"/>
     <brk id="137" min="0" max="16383" man="1"/>
@@ -7926,7 +7498,6 @@
     <brk id="997" min="0" max="16383" man="1"/>
     <brk id="1051" min="0" max="16383" man="1"/>
     <brk id="1071" min="0" max="16383" man="1"/>
-    <brk id="1125" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -7953,16 +7524,16 @@
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>These notes describe functions the wizard does not have. They are not bug reports: a defect is a gap between implemented behavior and the expected behavior, not a request for a new function.</t>
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>These notes describe functions the application does not have. They are not bug reports: a defect is a gap between implemented behavior and the expected behavior, not a request for a new function.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>IMP-001   The wizard never asks for a date, a time, or a dealership</t>
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>IMP-001   The application never asks for a date, a time, or a dealership</t>
         </is>
       </c>
     </row>
@@ -8003,7 +7574,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>IMP-002   Book does not ask for consent to use the name, age, and phone number</t>
         </is>
@@ -8054,161 +7625,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Photos of three models</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>S500 Cabriolet AMG is a cabriolet, GLC 250D 4MATIC is an SUV, and CLA SB Standard is a shooting brake. The body style in the photo matches the caption.</t>
-        </is>
-      </c>
-      <c r="C2" s="32" t="inlineStr">
-        <is>
-          <t>Not a defect</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Carousel with a pause between clicks</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>The forward arrow cycles through S500 Cabriolet AMG, Cayenne 400, GLC 250D 4MATIC, and CLA SB Standard. The back arrow from the first model opens the last one.</t>
-        </is>
-      </c>
-      <c r="C3" s="32" t="inlineStr">
-        <is>
-          <t>Not a defect</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Engine lists for S500 and CLA</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>S500 Cabriolet AMG: Petrol 3.0 and Petrol 3.5, transmission Automatic only. CLA SB Standard: Petrol 2.0 and Diesel 2.0, Automatic and Manual.</t>
-        </is>
-      </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>Not a defect</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Cyrillic names</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Last name Иванов, first name Иван, and middle name Иванович appear in the summary without corruption.</t>
-        </is>
-      </c>
-      <c r="C5" s="32" t="inlineStr">
-        <is>
-          <t>Not a defect</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Markup in a name</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>The value &lt;script&gt;alert(1)&lt;/script&gt; in the first name is shown as text. No dialog appeared.</t>
-        </is>
-      </c>
-      <c r="C6" s="32" t="inlineStr">
-        <is>
-          <t>Not a defect</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Path with ordinary data</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Ivanov / Ivan / Ivanovich / 30 / +375291234567 for S500 Cabriolet AMG reaches the thank-you screen. Copy issues on that path are BUG-014 and BUG-015.</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="inlineStr">
-        <is>
-          <t>Not a defect</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Console and width</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>The console had no messages on load. At 1440×900 and at 1280×800, a name of ordinary length does not cause a horizontal scrollbar.</t>
-        </is>
-      </c>
-      <c r="C8" s="32" t="inlineStr">
-        <is>
-          <t>Not a defect</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C8"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/bug-reports/Bug_Report_Test_Drive.xlsx
+++ b/bug-reports/Bug_Report_Test_Drive.xlsx
@@ -1253,15 +1253,15 @@
       </c>
       <c r="D6" s="6" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Author</t>
+          <t>Project description</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Your task is to find bugs in the system. Because there is no documentation, rely on common sense, accepted practice, and user experience. Anything that contradicts these three criteria is to be filed as a bug.</t>
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
@@ -1269,12 +1269,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>OS: Linux, desktop. Browser: Google Chrome 148.0.7778.96. Window: 1440×900, zoom 100%. URL: https://testdrive.andersenlab.com/. Page build: Last-Modified 23 Apr 2026 13:11:09 GMT. Desktop only.</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
@@ -1282,25 +1282,25 @@
     <row r="9" ht="36" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>OS: Linux, desktop. Browser: Google Chrome 148.0.7778.96. Window: 1440×900, zoom 100%. URL: https://testdrive.andersenlab.com/. Page build: Last-Modified 23 Apr 2026 13:11:09 GMT. Desktop only.</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>Out of scope</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Mobile layout, other browsers, saving the customer, and sending email. The last two were excluded by the test request.</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Report rules</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>One defect is one report. The title starts with the screen and names the observed failure. Each step is one action. The expected result describes what the customer should see and does not prescribe a fix.</t>
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
@@ -1308,15 +1308,28 @@
     <row r="11" ht="48" customHeight="1">
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>Report rules</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>One defect is one report. The title starts with the screen and names the observed failure. Each step is one action. The expected result describes what the customer should see and does not prescribe a fix.</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>Where to read</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Register is the filterable list. Bug reports is the full card for each defect, with screenshots. Improvements are observations that are not filed as defects.</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
@@ -1419,7 +1432,8 @@
     </row>
     <row r="23" ht="22" customHeight="1"/>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="C12:D12"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:D7"/>
@@ -2189,7 +2203,7 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>BUG-020</t>
+          <t>BUG-019</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
@@ -7192,7 +7206,7 @@
     <row r="1072" ht="28" customHeight="1">
       <c r="A1072" s="17" t="inlineStr">
         <is>
-          <t>BUG-020   [Thank you] After Book, the screen does not show what was booked</t>
+          <t>BUG-019   [Thank you] After Book, the screen does not show what was booked</t>
         </is>
       </c>
       <c r="B1072" s="18" t="n"/>
@@ -7205,7 +7219,7 @@
       </c>
       <c r="B1073" s="5" t="inlineStr">
         <is>
-          <t>BUG-020</t>
+          <t>BUG-019</t>
         </is>
       </c>
     </row>
